--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.83955710407569</v>
+        <v>5.4989280294123</v>
       </c>
       <c r="D2" t="n">
-        <v>26.48887490678228</v>
+        <v>4.30444217235212</v>
       </c>
       <c r="E2" t="n">
-        <v>15.42234446596269</v>
+        <v>2.506130975718937</v>
       </c>
       <c r="F2" t="n">
-        <v>9.322861409184656</v>
+        <v>1.514964978992506</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.76463673314043</v>
+        <v>7.274253469135321</v>
       </c>
       <c r="D3" t="n">
-        <v>33.39890383986765</v>
+        <v>5.427321873978493</v>
       </c>
       <c r="E3" t="n">
-        <v>15.42234446596269</v>
+        <v>2.506130975718937</v>
       </c>
       <c r="F3" t="n">
-        <v>9.322861409184656</v>
+        <v>1.514964978992506</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.15072311648068</v>
+        <v>3.436992506428111</v>
       </c>
       <c r="D4" t="n">
-        <v>33.36449892258852</v>
+        <v>5.421731074920634</v>
       </c>
       <c r="E4" t="n">
-        <v>15.42234446596269</v>
+        <v>2.506130975718937</v>
       </c>
       <c r="F4" t="n">
-        <v>9.322861409184656</v>
+        <v>1.514964978992506</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.17782019716661</v>
+        <v>6.203895782039575</v>
       </c>
       <c r="D5" t="n">
-        <v>11.06797181058933</v>
+        <v>1.798545419220766</v>
       </c>
       <c r="E5" t="n">
-        <v>15.42234446596269</v>
+        <v>2.506130975718937</v>
       </c>
       <c r="F5" t="n">
-        <v>9.322861409184656</v>
+        <v>1.514964978992506</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.33025646584483</v>
+        <v>3.791166675699785</v>
       </c>
       <c r="D6" t="n">
-        <v>13.58999077883623</v>
+        <v>2.208373501560888</v>
       </c>
       <c r="E6" t="n">
-        <v>15.42234446596269</v>
+        <v>2.506130975718937</v>
       </c>
       <c r="F6" t="n">
-        <v>9.322861409184656</v>
+        <v>1.514964978992506</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>58.06655839921365</v>
+        <v>9.435815739872218</v>
       </c>
       <c r="D7" t="n">
-        <v>31.37770029297856</v>
+        <v>5.098876297609016</v>
       </c>
       <c r="E7" t="n">
-        <v>15.42234446596269</v>
+        <v>2.506130975718937</v>
       </c>
       <c r="F7" t="n">
-        <v>9.322861409184656</v>
+        <v>1.514964978992506</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.22252344592801</v>
+        <v>2.311160059963302</v>
       </c>
       <c r="D8" t="n">
-        <v>33.7882417098285</v>
+        <v>5.490589277847131</v>
       </c>
       <c r="E8" t="n">
-        <v>15.42234446596269</v>
+        <v>2.506130975718937</v>
       </c>
       <c r="F8" t="n">
-        <v>9.322861409184656</v>
+        <v>1.514964978992506</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.76495182093961</v>
+        <v>7.599304670902687</v>
       </c>
       <c r="D9" t="n">
-        <v>14.92399735132696</v>
+        <v>2.425149569590631</v>
       </c>
       <c r="E9" t="n">
-        <v>15.42234446596269</v>
+        <v>2.506130975718937</v>
       </c>
       <c r="F9" t="n">
-        <v>9.322861409184656</v>
+        <v>1.514964978992506</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.94216919775641</v>
+        <v>4.540602494635417</v>
       </c>
       <c r="D10" t="n">
-        <v>29.72146101884067</v>
+        <v>4.829737415561609</v>
       </c>
       <c r="E10" t="n">
-        <v>15.42234446596269</v>
+        <v>2.506130975718937</v>
       </c>
       <c r="F10" t="n">
-        <v>9.322861409184656</v>
+        <v>1.514964978992506</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>51.14180682551084</v>
+        <v>8.310543609145512</v>
       </c>
       <c r="D11" t="n">
-        <v>6.285763451994558</v>
+        <v>1.021436560949116</v>
       </c>
       <c r="E11" t="n">
-        <v>15.42234446596269</v>
+        <v>2.506130975718937</v>
       </c>
       <c r="F11" t="n">
-        <v>9.322861409184656</v>
+        <v>1.514964978992506</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.96218818391493</v>
+        <v>7.956355579886176</v>
       </c>
       <c r="D12" t="n">
-        <v>26.28349335813807</v>
+        <v>4.271067670697436</v>
       </c>
       <c r="E12" t="n">
-        <v>15.42234446596269</v>
+        <v>2.506130975718937</v>
       </c>
       <c r="F12" t="n">
-        <v>9.322861409184656</v>
+        <v>1.514964978992506</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>67.78091766677213</v>
+        <v>11.01439912085047</v>
       </c>
       <c r="D13" t="n">
-        <v>22.16785666196497</v>
+        <v>3.602276707569308</v>
       </c>
       <c r="E13" t="n">
-        <v>15.42234446596269</v>
+        <v>2.506130975718937</v>
       </c>
       <c r="F13" t="n">
-        <v>9.322861409184656</v>
+        <v>1.514964978992506</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
